--- a/simulacaoes_/lote_eixos_1p5/simulacao_C_20/pre_sizing_results_optimized.xlsx
+++ b/simulacaoes_/lote_eixos_1p5/simulacao_C_20/pre_sizing_results_optimized.xlsx
@@ -497,2052 +497,2052 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>45.46294694412061</v>
+        <v>99.9999995697257</v>
       </c>
       <c r="B2" t="n">
-        <v>179.7022969785597</v>
+        <v>175.3039085201927</v>
       </c>
       <c r="C2" t="n">
-        <v>48.78068953429131</v>
+        <v>45.4348506625467</v>
       </c>
       <c r="D2" t="n">
-        <v>9.550076688722122</v>
+        <v>5.712490307396402</v>
       </c>
       <c r="E2" t="n">
-        <v>2.900956847144865</v>
+        <v>3.990350117587441</v>
       </c>
       <c r="F2" t="n">
-        <v>5.299371811680241</v>
+        <v>15.538715997247</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4741233527125679</v>
+        <v>0.02917635475192494</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.06798769222980565</v>
+        <v>-0.8896486050803456</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.5901601661563575</v>
+        <v>-0.9210079998736704</v>
       </c>
       <c r="J2" t="n">
-        <v>-7.179364291219533e-05</v>
+        <v>-0.9408576914867907</v>
       </c>
       <c r="K2" t="n">
-        <v>-4.537930701663205e-05</v>
+        <v>-9.404183545762455e-05</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.21461138380116</v>
+        <v>-0.5874999969342956</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.07681492415563022</v>
+        <v>-0.003967417282917107</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>45.46294694412061</v>
+        <v>47.59972549193003</v>
       </c>
       <c r="B3" t="n">
-        <v>179.8507247426453</v>
+        <v>172.1399104202384</v>
       </c>
       <c r="C3" t="n">
-        <v>48.78068953429131</v>
+        <v>45.4357535808355</v>
       </c>
       <c r="D3" t="n">
-        <v>9.550076688722122</v>
+        <v>9.898274078037646</v>
       </c>
       <c r="E3" t="n">
-        <v>4.498240970336952</v>
+        <v>2.526091602190318</v>
       </c>
       <c r="F3" t="n">
-        <v>5.299371811680241</v>
+        <v>5.631677718249779</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4741233527125679</v>
+        <v>0.3914046376228014</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.06798769222980565</v>
+        <v>-0.06735794575260122</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.5901601661563575</v>
+        <v>-0.5896527409102807</v>
       </c>
       <c r="J3" t="n">
-        <v>-7.179364291219533e-05</v>
+        <v>-0.000296229902751674</v>
       </c>
       <c r="K3" t="n">
-        <v>-4.537930701663205e-05</v>
+        <v>-1.287354696606363e-05</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.21461138380116</v>
+        <v>-0.2141480441300014</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.07681492415563022</v>
+        <v>-0.004164417636837864</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>99.99999999581799</v>
+        <v>99.9999995697257</v>
       </c>
       <c r="B4" t="n">
-        <v>197.4139360822329</v>
+        <v>171.9590075884363</v>
       </c>
       <c r="C4" t="n">
-        <v>48.7803585378679</v>
+        <v>45.4348506625467</v>
       </c>
       <c r="D4" t="n">
-        <v>5.000000076082902</v>
+        <v>5.712490307396402</v>
       </c>
       <c r="E4" t="n">
-        <v>4.446577937728515</v>
+        <v>3.73683552627029</v>
       </c>
       <c r="F4" t="n">
-        <v>15.28933488442479</v>
+        <v>15.538715997247</v>
       </c>
       <c r="G4" t="n">
-        <v>0.02959046806400347</v>
+        <v>0.02917635475192494</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9027316402964674</v>
+        <v>-0.8896486050803456</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.9287003764458769</v>
+        <v>-0.9210079998736704</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.9498736637413959</v>
+        <v>-0.9408576914867907</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.008560727203918336</v>
+        <v>-9.404183545762455e-05</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.6220069729627962</v>
+        <v>-0.5874999969342956</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.07679231954751692</v>
+        <v>-0.003967417282917107</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>45.79398325979365</v>
+        <v>69.8326001063127</v>
       </c>
       <c r="B5" t="n">
-        <v>181.0855291447071</v>
+        <v>162.7877429098987</v>
       </c>
       <c r="C5" t="n">
-        <v>48.83732851615532</v>
+        <v>45.44015552509542</v>
       </c>
       <c r="D5" t="n">
-        <v>9.554399822267037</v>
+        <v>8.581439033076046</v>
       </c>
       <c r="E5" t="n">
-        <v>4.300910930800571</v>
+        <v>2.584895223467283</v>
       </c>
       <c r="F5" t="n">
-        <v>5.3456383095459</v>
+        <v>8.999805965134298</v>
       </c>
       <c r="G5" t="n">
-        <v>0.4614399932180582</v>
+        <v>0.09650092359850147</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.08763669749885152</v>
+        <v>-0.6956635031572025</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5965658422138114</v>
+        <v>-0.8240128050180724</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.027976072184713</v>
+        <v>-0.7739052075822176</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.006506754768419235</v>
+        <v>-0.04705769562217472</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.2170842481623802</v>
+        <v>-0.3725572757574779</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.08068294779107162</v>
+        <v>-0.005124841839001526</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>51.79773792197754</v>
+        <v>65.35083037719539</v>
       </c>
       <c r="B6" t="n">
-        <v>142.1246145267521</v>
+        <v>173.0875069159876</v>
       </c>
       <c r="C6" t="n">
-        <v>48.84418284869759</v>
+        <v>47.12723122679952</v>
       </c>
       <c r="D6" t="n">
-        <v>9.226419519223816</v>
+        <v>8.558273141636521</v>
       </c>
       <c r="E6" t="n">
-        <v>4.460651846273178</v>
+        <v>2.953706441468944</v>
       </c>
       <c r="F6" t="n">
-        <v>6.085726257097246</v>
+        <v>8.215573427725067</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2901830819606285</v>
+        <v>0.1220140404604597</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.3650852497631035</v>
+        <v>-0.6313313756825911</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.6921627152302038</v>
+        <v>-0.7960319601290654</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.3995943313776255</v>
+        <v>-0.7084831032726649</v>
       </c>
       <c r="K6" t="n">
-        <v>-0.0209166666548106</v>
+        <v>-0.002317767461909085</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.2619327141303484</v>
+        <v>-0.3406246664375171</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.08115104801826657</v>
+        <v>-0.3732140858471686</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>53.16063177378844</v>
+        <v>53.79659658977763</v>
       </c>
       <c r="B7" t="n">
-        <v>142.1246145267521</v>
+        <v>184.6903576518492</v>
       </c>
       <c r="C7" t="n">
-        <v>48.57785265845098</v>
+        <v>45.43037955433556</v>
       </c>
       <c r="D7" t="n">
-        <v>9.226419519223816</v>
+        <v>9.574063441704892</v>
       </c>
       <c r="E7" t="n">
-        <v>4.460651846273178</v>
+        <v>2.408185424353903</v>
       </c>
       <c r="F7" t="n">
-        <v>6.29421606217793</v>
+        <v>6.440148466209571</v>
       </c>
       <c r="G7" t="n">
-        <v>0.263798665482867</v>
+        <v>0.2476532195241266</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4114390629640117</v>
+        <v>-0.3495099115998001</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.709178566892543</v>
+        <v>-0.6862967742963462</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.4570531829947388</v>
+        <v>-0.3806545114307529</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.03516130841443289</v>
+        <v>-0.01564492448282319</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.2721136262378828</v>
+        <v>-0.2583007507021656</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.06836424746617809</v>
+        <v>-0.00299190276412245</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>84.22437388711053</v>
+        <v>61.04265216463841</v>
       </c>
       <c r="B8" t="n">
-        <v>180.214715351286</v>
+        <v>184.6903576518492</v>
       </c>
       <c r="C8" t="n">
-        <v>49.50851390178595</v>
+        <v>45.43050485375198</v>
       </c>
       <c r="D8" t="n">
-        <v>6.902914694609772</v>
+        <v>9.309457883306679</v>
       </c>
       <c r="E8" t="n">
-        <v>2.850064902360685</v>
+        <v>2.408185424353903</v>
       </c>
       <c r="F8" t="n">
-        <v>11.70442652817197</v>
+        <v>7.551638962452226</v>
       </c>
       <c r="G8" t="n">
-        <v>0.0516462080917002</v>
+        <v>0.156139367491649</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8434551730621412</v>
+        <v>-0.5503164459412166</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8955097009704319</v>
+        <v>-0.7625853545948461</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.9060674012546023</v>
+        <v>-0.6205748345953647</v>
       </c>
       <c r="K8" t="n">
-        <v>-0.09144157811969351</v>
+        <v>-0.06334885283843018</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.5041619458972837</v>
+        <v>-0.3099288966730487</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.1065144378209272</v>
+        <v>-0.003019240818612628</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>59.15386068850015</v>
+        <v>81.07069502518202</v>
       </c>
       <c r="B9" t="n">
-        <v>178.1436933585257</v>
+        <v>173.0875069159876</v>
       </c>
       <c r="C9" t="n">
-        <v>47.45485319485591</v>
+        <v>45.43608209844103</v>
       </c>
       <c r="D9" t="n">
-        <v>9.020878660590959</v>
+        <v>8.640867041922451</v>
       </c>
       <c r="E9" t="n">
-        <v>2.240266878857672</v>
+        <v>2.953706441468944</v>
       </c>
       <c r="F9" t="n">
-        <v>7.173578681502456</v>
+        <v>11.41167159830652</v>
       </c>
       <c r="G9" t="n">
-        <v>0.1781762505874244</v>
+        <v>0.05812363802943726</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.569067592122235</v>
+        <v>-0.8010689520901352</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.7702970396413601</v>
+        <v>-0.8735291830524967</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.6410038491692958</v>
+        <v>-0.8711597889366943</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.05937186696081304</v>
+        <v>-0.2472590853869794</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.316883464138274</v>
+        <v>-0.4526287020544218</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.08737011747051319</v>
+        <v>-0.004236094205314761</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>94.0899924424301</v>
+        <v>62.96525363052197</v>
       </c>
       <c r="B10" t="n">
-        <v>140.0954830500504</v>
+        <v>184.6903576518492</v>
       </c>
       <c r="C10" t="n">
-        <v>48.78270685864566</v>
+        <v>45.43050485375198</v>
       </c>
       <c r="D10" t="n">
-        <v>6.056637658501346</v>
+        <v>8.975724275152487</v>
       </c>
       <c r="E10" t="n">
-        <v>2.55613323760761</v>
+        <v>2.522945153715895</v>
       </c>
       <c r="F10" t="n">
-        <v>13.94508132325292</v>
+        <v>7.806821054232731</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0359628438222593</v>
+        <v>0.1393149221103602</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.884977960212178</v>
+        <v>-0.589360929964477</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9183372404636241</v>
+        <v>-0.7785125019816731</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.9374649860297293</v>
+        <v>-0.6636888143283922</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.1288263626528686</v>
+        <v>-0.02236165820117698</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.5778588044345144</v>
+        <v>-0.323627432117469</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.07695269249161034</v>
+        <v>-0.003019240818612628</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>73.15242024557948</v>
+        <v>90.14700827542336</v>
       </c>
       <c r="B11" t="n">
-        <v>188.0649643558072</v>
+        <v>94.0003899678693</v>
       </c>
       <c r="C11" t="n">
-        <v>49.78285495216544</v>
+        <v>45.43588834845047</v>
       </c>
       <c r="D11" t="n">
-        <v>7.804211663902755</v>
+        <v>7.256870888915982</v>
       </c>
       <c r="E11" t="n">
-        <v>2.335194772176423</v>
+        <v>3.740576412532419</v>
       </c>
       <c r="F11" t="n">
-        <v>9.492670504066741</v>
+        <v>13.26904565187021</v>
       </c>
       <c r="G11" t="n">
-        <v>0.08344572153042738</v>
+        <v>0.04073274846450102</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.7666234125766721</v>
+        <v>-0.8526993790703983</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.8568825739094346</v>
+        <v>-0.9003713374723351</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.8407375898190051</v>
+        <v>-0.9134058127925742</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.07635197766092124</v>
+        <v>-0.1476755282303809</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.4214536801483797</v>
+        <v>-0.5172974339623914</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.09578212689795737</v>
+        <v>-0.004193821480102666</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>92.99116739599248</v>
+        <v>79.48126826030649</v>
       </c>
       <c r="B12" t="n">
-        <v>177.9865876309846</v>
+        <v>173.5636552982065</v>
       </c>
       <c r="C12" t="n">
-        <v>48.88624718920408</v>
+        <v>45.43387642684113</v>
       </c>
       <c r="D12" t="n">
-        <v>5.776279736962072</v>
+        <v>7.708030399468655</v>
       </c>
       <c r="E12" t="n">
-        <v>4.418269451288569</v>
+        <v>3.609881801026779</v>
       </c>
       <c r="F12" t="n">
-        <v>13.5892521952321</v>
+        <v>10.82194367728436</v>
       </c>
       <c r="G12" t="n">
-        <v>0.03727058864609197</v>
+        <v>0.06169036957644002</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.8812596808090818</v>
+        <v>-0.7900188665970663</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.9162514063842194</v>
+        <v>-0.8681920857956139</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.9347916806964813</v>
+        <v>-0.8616736106763301</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.004600088463496128</v>
+        <v>-0.02127596982828193</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5696505047166203</v>
+        <v>-0.4413040363546837</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.08402373142347004</v>
+        <v>-0.003754856765337128</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>56.6115192513773</v>
+        <v>50.14535490716323</v>
       </c>
       <c r="B13" t="n">
-        <v>136.3927279991204</v>
+        <v>177.272108992638</v>
       </c>
       <c r="C13" t="n">
-        <v>48.82841182836376</v>
+        <v>45.42163495762825</v>
       </c>
       <c r="D13" t="n">
-        <v>9.010901292541202</v>
+        <v>9.810331776171427</v>
       </c>
       <c r="E13" t="n">
-        <v>2.036969931559777</v>
+        <v>2.587207781494816</v>
       </c>
       <c r="F13" t="n">
-        <v>6.763135042919137</v>
+        <v>5.961117737499569</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2089292129475308</v>
+        <v>0.3219344965233961</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.510403186944598</v>
+        <v>-0.2000746838235562</v>
       </c>
       <c r="I13" t="n">
-        <v>-0.7469478249392785</v>
+        <v>-0.6338522932351303</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.5747981151619789</v>
+        <v>-0.1847909511168855</v>
       </c>
       <c r="K13" t="n">
-        <v>-0.04551786991671641</v>
+        <v>-0.01479045399796427</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.2978919963256496</v>
+        <v>-0.232285653713538</v>
       </c>
       <c r="M13" t="n">
-        <v>-0.08007400395076054</v>
+        <v>-0.001083990755253866</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>78.90069482029166</v>
+        <v>48.98202938582207</v>
       </c>
       <c r="B14" t="n">
-        <v>184.6487248639151</v>
+        <v>172.1556032104187</v>
       </c>
       <c r="C14" t="n">
-        <v>47.62427937222608</v>
+        <v>45.43468721809046</v>
       </c>
       <c r="D14" t="n">
-        <v>7.242088764063904</v>
+        <v>9.89276022373873</v>
       </c>
       <c r="E14" t="n">
-        <v>4.998529577277705</v>
+        <v>2.972550795872313</v>
       </c>
       <c r="F14" t="n">
-        <v>10.55953419509449</v>
+        <v>5.819006633150147</v>
       </c>
       <c r="G14" t="n">
-        <v>0.0642617773229494</v>
+        <v>0.3516850649987776</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.8118736824906404</v>
+        <v>-0.1427167818484344</v>
       </c>
       <c r="I14" t="n">
-        <v>-0.8791712612593625</v>
+        <v>-0.6144880891448894</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.8802536286015211</v>
+        <v>-0.1061799532052093</v>
       </c>
       <c r="K14" t="n">
-        <v>-0.01579059497788561</v>
+        <v>-0.0165164900642053</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.4643936920483229</v>
+        <v>-0.2239969593739821</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.08548380960119589</v>
+        <v>-0.003931756674282194</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>49.42539968908049</v>
+        <v>92.67612626705736</v>
       </c>
       <c r="B15" t="n">
-        <v>156.0949052754605</v>
+        <v>184.3636328493004</v>
       </c>
       <c r="C15" t="n">
-        <v>48.83881891452296</v>
+        <v>45.42164133320274</v>
       </c>
       <c r="D15" t="n">
-        <v>9.290041446108033</v>
+        <v>6.911530583689007</v>
       </c>
       <c r="E15" t="n">
-        <v>2.668796413413435</v>
+        <v>2.587207781494816</v>
       </c>
       <c r="F15" t="n">
-        <v>5.764479057187614</v>
+        <v>13.83745949878517</v>
       </c>
       <c r="G15" t="n">
-        <v>0.3455730204108703</v>
+        <v>0.03722111900519943</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.2714925035703208</v>
+        <v>-0.8636805739447434</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.6588014612892948</v>
+        <v>-0.9063573134561124</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.2792953688910194</v>
+        <v>-0.9218285123929499</v>
       </c>
       <c r="K15" t="n">
-        <v>-0.0006593678378067892</v>
+        <v>-0.1259968542003671</v>
       </c>
       <c r="L15" t="n">
-        <v>-0.2442111821076039</v>
+        <v>-0.5353173996527836</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.08078473097859593</v>
+        <v>-0.001085381789689838</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>65.72529890612483</v>
+        <v>49.59582667971424</v>
       </c>
       <c r="B16" t="n">
-        <v>139.8280556321324</v>
+        <v>117.7600678178058</v>
       </c>
       <c r="C16" t="n">
-        <v>48.83042336453078</v>
+        <v>45.43152371287368</v>
       </c>
       <c r="D16" t="n">
-        <v>8.374851612807023</v>
+        <v>9.85110247424355</v>
       </c>
       <c r="E16" t="n">
-        <v>4.188562349219124</v>
+        <v>2.346840310037249</v>
       </c>
       <c r="F16" t="n">
-        <v>8.167956847100864</v>
+        <v>5.894157234020701</v>
       </c>
       <c r="G16" t="n">
-        <v>0.1215841670753676</v>
+        <v>0.3355715995912512</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.6826424305600245</v>
+        <v>-0.1857685892669906</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.8183432086352151</v>
+        <v>-0.6313375129415717</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.7607356349968309</v>
+        <v>-0.1683674114910694</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.05352116638272397</v>
+        <v>-0.04962113366827135</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.3659725658499255</v>
+        <v>-0.2469687000978569</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.08021137699634653</v>
+        <v>-0.003241537354257973</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>71.44441093064172</v>
+        <v>73.58280151820779</v>
       </c>
       <c r="B17" t="n">
-        <v>112.3711309468308</v>
+        <v>172.1290011479221</v>
       </c>
       <c r="C17" t="n">
-        <v>48.99537499480961</v>
+        <v>45.43932333549295</v>
       </c>
       <c r="D17" t="n">
-        <v>7.831417922780315</v>
+        <v>8.634175442034358</v>
       </c>
       <c r="E17" t="n">
-        <v>4.194614711212105</v>
+        <v>2.953706441468944</v>
       </c>
       <c r="F17" t="n">
-        <v>9.138873581453952</v>
+        <v>9.773056097066601</v>
       </c>
       <c r="G17" t="n">
-        <v>0.09047828488399003</v>
+        <v>0.08062471312468822</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7503997537049381</v>
+        <v>-0.7379796993299078</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.8492085952274741</v>
+        <v>-0.8432341448773153</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.8259352863117232</v>
+        <v>-0.8145408494167025</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.03444254578093169</v>
+        <v>-0.1212163735284455</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.408694731466407</v>
+        <v>-0.3992774608172305</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.09046902869960564</v>
+        <v>-0.004943273198461939</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>48.83257523159983</v>
+        <v>78.47477867369206</v>
       </c>
       <c r="B18" t="n">
-        <v>196.7457581115414</v>
+        <v>141.2996232774531</v>
       </c>
       <c r="C18" t="n">
-        <v>48.94866229326889</v>
+        <v>45.43387642684113</v>
       </c>
       <c r="D18" t="n">
-        <v>9.408754454189479</v>
+        <v>7.708030399468655</v>
       </c>
       <c r="E18" t="n">
-        <v>4.671948637580288</v>
+        <v>3.609881801026779</v>
       </c>
       <c r="F18" t="n">
-        <v>5.717910896236353</v>
+        <v>10.59718941900624</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3621127909065436</v>
+        <v>0.06437677775305667</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.2449158721098209</v>
+        <v>-0.7822979742582327</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.6495071898090559</v>
+        <v>-0.8644195319181956</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2440915565538908</v>
+        <v>-0.8549114917342518</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.01964502991042238</v>
+        <v>-0.0002201489700236109</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.2397827420726093</v>
+        <v>-0.4341327980500559</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.08828622149278033</v>
+        <v>-0.003754856765337128</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>55.43654924386198</v>
+        <v>50.83803012367856</v>
       </c>
       <c r="B19" t="n">
-        <v>150.0533825524522</v>
+        <v>174.4743988728661</v>
       </c>
       <c r="C19" t="n">
-        <v>48.83732851615532</v>
+        <v>45.43046242391618</v>
       </c>
       <c r="D19" t="n">
-        <v>9.283203720208689</v>
+        <v>9.730227873732506</v>
       </c>
       <c r="E19" t="n">
-        <v>4.295281170179525</v>
+        <v>3.329132309097392</v>
       </c>
       <c r="F19" t="n">
-        <v>6.647272034733713</v>
+        <v>6.04082155801849</v>
       </c>
       <c r="G19" t="n">
-        <v>0.2262432012598934</v>
+        <v>0.3056699214195103</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.4791666795265054</v>
+        <v>-0.2318418337388109</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.7347545440540073</v>
+        <v>-0.6447603014072419</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.5383572733081142</v>
+        <v>-0.2275538963917081</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.08408266801440066</v>
+        <v>-0.007883644271975229</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.2891148884389216</v>
+        <v>-0.2372209646312098</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.08068294779107162</v>
+        <v>-0.003009983399895749</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>46.71291261483663</v>
+        <v>95.90990222184328</v>
       </c>
       <c r="B20" t="n">
-        <v>139.0495778874368</v>
+        <v>199.8026335082452</v>
       </c>
       <c r="C20" t="n">
-        <v>48.84298561670256</v>
+        <v>47.10750717511468</v>
       </c>
       <c r="D20" t="n">
-        <v>9.564809384049619</v>
+        <v>6.073362649152939</v>
       </c>
       <c r="E20" t="n">
-        <v>2.357307881285668</v>
+        <v>2.136084173046701</v>
       </c>
       <c r="F20" t="n">
-        <v>5.467829007342782</v>
+        <v>14.54931422690497</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4282949255119787</v>
+        <v>0.03330444420680228</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.139406589546276</v>
+        <v>-0.8761344230718984</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.6136538335184232</v>
+        <v>-0.9133012693983971</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.1005623916417251</v>
+        <v>-0.9311191748254858</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.02101246900304649</v>
+        <v>-0.01373145127223652</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.2239487145214403</v>
+        <v>-0.5583580533306334</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.08106928592612701</v>
+        <v>-0.3689106563886588</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>61.68277704240937</v>
+        <v>67.37167306132966</v>
       </c>
       <c r="B21" t="n">
-        <v>174.805159778467</v>
+        <v>116.5284376036674</v>
       </c>
       <c r="C21" t="n">
-        <v>48.80025004823337</v>
+        <v>45.42695291624378</v>
       </c>
       <c r="D21" t="n">
-        <v>9.356569864502722</v>
+        <v>9.114196520701011</v>
       </c>
       <c r="E21" t="n">
-        <v>4.991417063608823</v>
+        <v>3.512257019887222</v>
       </c>
       <c r="F21" t="n">
-        <v>7.690555904459304</v>
+        <v>8.652541498641202</v>
       </c>
       <c r="G21" t="n">
-        <v>0.1538368897436771</v>
+        <v>0.1098680229924394</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.6179211367092194</v>
+        <v>-0.6621372339736069</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.7903366219101452</v>
+        <v>-0.8091717996940629</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6938688054459734</v>
+        <v>-0.7402720885866078</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.1845425869648706</v>
+        <v>-0.1177788477955464</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.3357746456431625</v>
+        <v>-0.3550231705619739</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.07815076261457311</v>
+        <v>-0.002244272635007205</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>50.06902600256291</v>
+        <v>57.64971956478406</v>
       </c>
       <c r="B22" t="n">
-        <v>134.8837371809519</v>
+        <v>182.519179810231</v>
       </c>
       <c r="C22" t="n">
-        <v>48.78065055184571</v>
+        <v>45.43752670512684</v>
       </c>
       <c r="D22" t="n">
-        <v>9.281915665057817</v>
+        <v>9.324678357094676</v>
       </c>
       <c r="E22" t="n">
-        <v>2.335047640976511</v>
+        <v>2.268160868678849</v>
       </c>
       <c r="F22" t="n">
-        <v>5.849521529047133</v>
+        <v>6.986401268341654</v>
       </c>
       <c r="G22" t="n">
-        <v>0.3292580037966453</v>
+        <v>0.1918990743518269</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2986481874827666</v>
+        <v>-0.4688929558435784</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.668348227073045</v>
+        <v>-0.7307177289615575</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.3147605115443948</v>
+        <v>-0.5268561571567301</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.006847301167261473</v>
+        <v>-0.01789072653359945</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.249019115549342</v>
+        <v>-0.2857542518990864</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.07681226194285826</v>
+        <v>-0.004551281118581885</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>47.57405617593575</v>
+        <v>63.73814870879059</v>
       </c>
       <c r="B23" t="n">
-        <v>147.0148473229539</v>
+        <v>170.1521013315972</v>
       </c>
       <c r="C23" t="n">
-        <v>48.92885239252718</v>
+        <v>45.43071955564577</v>
       </c>
       <c r="D23" t="n">
-        <v>9.407251325919463</v>
+        <v>8.961638541207451</v>
       </c>
       <c r="E23" t="n">
-        <v>2.884906435136556</v>
+        <v>2.888853155679016</v>
       </c>
       <c r="F23" t="n">
-        <v>5.546305534045767</v>
+        <v>7.941818930343199</v>
       </c>
       <c r="G23" t="n">
-        <v>0.3992042535974812</v>
+        <v>0.1333905073095207</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1847611347306035</v>
+        <v>-0.6036273956164091</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6289373217892903</v>
+        <v>-0.7844056014579728</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.163075296922237</v>
+        <v>-0.6790895690064747</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.001649666238993471</v>
+        <v>-0.03129041789663596</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.23038151697034</v>
+        <v>-0.329134309550133</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.08693335175955244</v>
+        <v>-0.003066084868166702</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>67.61344775250214</v>
+        <v>76.09819031958227</v>
       </c>
       <c r="B24" t="n">
-        <v>141.7924810781061</v>
+        <v>170.0691598600669</v>
       </c>
       <c r="C24" t="n">
-        <v>48.8920712916517</v>
+        <v>45.42163495762825</v>
       </c>
       <c r="D24" t="n">
-        <v>8.263785515952941</v>
+        <v>8.079260009537325</v>
       </c>
       <c r="E24" t="n">
-        <v>2.343850846689313</v>
+        <v>2.587207781494816</v>
       </c>
       <c r="F24" t="n">
-        <v>8.49596372469674</v>
+        <v>10.1683961499766</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1099726811879184</v>
+        <v>0.07159734744807002</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.7075036173656699</v>
+        <v>-0.7622308191468935</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.829429625998191</v>
+        <v>-0.8547140597779667</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.7852430893042321</v>
+        <v>-0.8369441271598291</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.06273594788867135</v>
+        <v>-0.04425304771411365</v>
       </c>
       <c r="L24" t="n">
-        <v>-0.3800771693928703</v>
+        <v>-0.4171996060270237</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.08442147455339971</v>
+        <v>-0.001083990755253866</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>46.71291261483663</v>
+        <v>56.81240654700525</v>
       </c>
       <c r="B25" t="n">
-        <v>139.0495778874368</v>
+        <v>171.7778310167759</v>
       </c>
       <c r="C25" t="n">
-        <v>48.84298561670256</v>
+        <v>45.42974424145017</v>
       </c>
       <c r="D25" t="n">
-        <v>9.564809384049619</v>
+        <v>9.371469970930663</v>
       </c>
       <c r="E25" t="n">
-        <v>4.998374425178178</v>
+        <v>2.653608781371309</v>
       </c>
       <c r="F25" t="n">
-        <v>5.467829007342782</v>
+        <v>6.861996847454309</v>
       </c>
       <c r="G25" t="n">
-        <v>0.4282949255119787</v>
+        <v>0.2024604274366647</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.139406589546276</v>
+        <v>-0.4456732801171937</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.6136538335184232</v>
+        <v>-0.7218758847982319</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1005623916417251</v>
+        <v>-0.4992012593141553</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.02101246900304649</v>
+        <v>-0.01558821939843152</v>
       </c>
       <c r="L25" t="n">
-        <v>-0.2239487145214403</v>
+        <v>-0.2797883966474124</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.08106928592612701</v>
+        <v>-0.002853289043672491</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>81.05615773777218</v>
+        <v>97.13238715919135</v>
       </c>
       <c r="B26" t="n">
-        <v>169.5421453078627</v>
+        <v>154.9196283372389</v>
       </c>
       <c r="C26" t="n">
-        <v>47.33325762389671</v>
+        <v>45.43286333058408</v>
       </c>
       <c r="D26" t="n">
-        <v>7.339673120725946</v>
+        <v>6.862279074479425</v>
       </c>
       <c r="E26" t="n">
-        <v>2.344941699678163</v>
+        <v>2.356005980257344</v>
       </c>
       <c r="F26" t="n">
-        <v>11.0618516015098</v>
+        <v>15.02156792359093</v>
       </c>
       <c r="G26" t="n">
-        <v>0.05876693898671306</v>
+        <v>0.03209514815205562</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.8255836926235263</v>
+        <v>-0.8802704525949425</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.8861480318588799</v>
+        <v>-0.9155792607192882</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.891640395172241</v>
+        <v>-0.9341243863380806</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.08590893211061522</v>
+        <v>-0.2310620356509786</v>
       </c>
       <c r="L26" t="n">
-        <v>-0.4804951503422032</v>
+        <v>-0.5670682585092384</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.08325637890813301</v>
+        <v>-0.003533817581981152</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>50.51702650526047</v>
+        <v>48.47795348302122</v>
       </c>
       <c r="B27" t="n">
-        <v>158.0065715157187</v>
+        <v>161.8887047023945</v>
       </c>
       <c r="C27" t="n">
-        <v>47.2457179108914</v>
+        <v>45.43384274624977</v>
       </c>
       <c r="D27" t="n">
-        <v>9.546894744554802</v>
+        <v>9.898274078037646</v>
       </c>
       <c r="E27" t="n">
-        <v>4.417466981404537</v>
+        <v>2.199284489862293</v>
       </c>
       <c r="F27" t="n">
-        <v>5.972470320170632</v>
+        <v>5.750862321318278</v>
       </c>
       <c r="G27" t="n">
-        <v>0.3195056138354246</v>
+        <v>0.3655465922851236</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3162159165933562</v>
+        <v>-0.1162168121029422</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.6744858463357417</v>
+        <v>-0.6056833842237664</v>
       </c>
       <c r="J27" t="n">
-        <v>-0.3373395811065036</v>
+        <v>-0.0692812598083901</v>
       </c>
       <c r="K27" t="n">
-        <v>-0.03697096953537825</v>
+        <v>-0.01116548839087722</v>
       </c>
       <c r="L27" t="n">
-        <v>-0.2523657105435412</v>
+        <v>-0.2204054185665262</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.08008410060046396</v>
+        <v>-0.003747508272678307</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>81.05615773777218</v>
+        <v>66.93631067119011</v>
       </c>
       <c r="B28" t="n">
-        <v>169.5421453078627</v>
+        <v>193.1456972315204</v>
       </c>
       <c r="C28" t="n">
-        <v>47.33325762389671</v>
+        <v>45.43050485375198</v>
       </c>
       <c r="D28" t="n">
-        <v>7.339673120725946</v>
+        <v>8.975724275152487</v>
       </c>
       <c r="E28" t="n">
-        <v>2.904125545391809</v>
+        <v>2.327932133535063</v>
       </c>
       <c r="F28" t="n">
-        <v>11.0618516015098</v>
+        <v>8.536081893298604</v>
       </c>
       <c r="G28" t="n">
-        <v>0.05876693898671306</v>
+        <v>0.112252851061805</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.8255836926235263</v>
+        <v>-0.6558841283693759</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.8861480318588799</v>
+        <v>-0.8064978525665094</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.891640395172241</v>
+        <v>-0.733906131316447</v>
       </c>
       <c r="K28" t="n">
-        <v>-0.08590893211061522</v>
+        <v>-0.08376803305613519</v>
       </c>
       <c r="L28" t="n">
-        <v>-0.4804951503422032</v>
+        <v>-0.3519212135322295</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.08325637890813301</v>
+        <v>-0.003019240818612628</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>64.72545276817323</v>
+        <v>59.24873092012655</v>
       </c>
       <c r="B29" t="n">
-        <v>138.0090030385888</v>
+        <v>144.8896263758562</v>
       </c>
       <c r="C29" t="n">
-        <v>48.8920712916517</v>
+        <v>45.43822727846046</v>
       </c>
       <c r="D29" t="n">
-        <v>8.235645673433377</v>
+        <v>9.255122823311435</v>
       </c>
       <c r="E29" t="n">
-        <v>2.273981023297267</v>
+        <v>2.817148774936836</v>
       </c>
       <c r="F29" t="n">
-        <v>7.952530282383409</v>
+        <v>7.233624632525848</v>
       </c>
       <c r="G29" t="n">
-        <v>0.1281781942667732</v>
+        <v>0.1737080462799073</v>
       </c>
       <c r="H29" t="n">
-        <v>-0.6684419713960642</v>
+        <v>-0.5096600743050586</v>
       </c>
       <c r="I29" t="n">
-        <v>-0.8121551340605184</v>
+        <v>-0.7465052146921942</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.7464740637016728</v>
+        <v>-0.5744378966347435</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.004682568682232821</v>
+        <v>-0.02640728369497016</v>
       </c>
       <c r="L29" t="n">
-        <v>-0.3585036454802153</v>
+        <v>-0.2971472078059016</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.08442147455339971</v>
+        <v>-0.00470413348228213</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>60.6867950747398</v>
+        <v>58.77330034161167</v>
       </c>
       <c r="B30" t="n">
-        <v>153.1627928171517</v>
+        <v>104.3119523668508</v>
       </c>
       <c r="C30" t="n">
-        <v>48.89385523692785</v>
+        <v>45.43946268735141</v>
       </c>
       <c r="D30" t="n">
-        <v>8.577442140960061</v>
+        <v>8.967966743283824</v>
       </c>
       <c r="E30" t="n">
-        <v>4.234454941941845</v>
+        <v>2.57256370675587</v>
       </c>
       <c r="F30" t="n">
-        <v>7.327870433587754</v>
+        <v>7.083900541322294</v>
       </c>
       <c r="G30" t="n">
-        <v>0.16178353816839</v>
+        <v>0.1782859445789096</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.600311361956586</v>
+        <v>-0.5049840653790301</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.783192955354952</v>
+        <v>-0.746242565330161</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.6751796145675139</v>
+        <v>-0.5704738338197053</v>
       </c>
       <c r="K30" t="n">
-        <v>-0.01560303488456236</v>
+        <v>-0.003846679182080117</v>
       </c>
       <c r="L30" t="n">
-        <v>-0.3283345908949075</v>
+        <v>-0.3157997525620875</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.08454330482409621</v>
+        <v>-0.004973677240306118</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>95.97881023286322</v>
+        <v>54.47598467884868</v>
       </c>
       <c r="B31" t="n">
-        <v>144.3465304476375</v>
+        <v>172.1290011479221</v>
       </c>
       <c r="C31" t="n">
-        <v>48.48248521515497</v>
+        <v>45.43943752039602</v>
       </c>
       <c r="D31" t="n">
-        <v>6.099194633090689</v>
+        <v>9.569045842461028</v>
       </c>
       <c r="E31" t="n">
-        <v>2.51579926766938</v>
+        <v>2.953706441468944</v>
       </c>
       <c r="F31" t="n">
-        <v>14.47233936366029</v>
+        <v>6.543377309967543</v>
       </c>
       <c r="G31" t="n">
-        <v>0.03379858058948008</v>
+        <v>0.2365068441824289</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.8910541457672565</v>
+        <v>-0.3729667513813683</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.921809511525844</v>
+        <v>-0.6948143763436236</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9417805674611313</v>
+        <v>-0.4101274026676299</v>
       </c>
       <c r="K31" t="n">
-        <v>-0.1974563417345713</v>
+        <v>-0.02406544264267301</v>
       </c>
       <c r="L31" t="n">
-        <v>-0.5919684050362017</v>
+        <v>-0.2631413908367968</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.06537682279228609</v>
+        <v>-0.004968186268223401</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>88.70605788786084</v>
+        <v>71.54144609617506</v>
       </c>
       <c r="B32" t="n">
-        <v>156.8411618252094</v>
+        <v>170.042099525759</v>
       </c>
       <c r="C32" t="n">
-        <v>48.78078256602937</v>
+        <v>45.4363076355162</v>
       </c>
       <c r="D32" t="n">
-        <v>6.278553224460771</v>
+        <v>8.307719068024339</v>
       </c>
       <c r="E32" t="n">
-        <v>2.335194772176423</v>
+        <v>2.716478541786045</v>
       </c>
       <c r="F32" t="n">
-        <v>12.61964737647858</v>
+        <v>9.274003630738656</v>
       </c>
       <c r="G32" t="n">
-        <v>0.043449224004453</v>
+        <v>0.08856108008607953</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8646452045984351</v>
+        <v>-0.7162364132593718</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.9069744679358007</v>
+        <v>-0.8333169794041938</v>
       </c>
       <c r="J32" t="n">
-        <v>-0.9224884986353125</v>
+        <v>-0.7939412266097212</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.02372494926203422</v>
+        <v>-0.01412786209099624</v>
       </c>
       <c r="L32" t="n">
-        <v>-0.5376404378904467</v>
+        <v>-0.3847328034352474</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.0768212775354023</v>
+        <v>-0.004285302294443072</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>90.44492702619171</v>
+        <v>55.08096532447647</v>
       </c>
       <c r="B33" t="n">
-        <v>155.6615210069884</v>
+        <v>197.30012927457</v>
       </c>
       <c r="C33" t="n">
-        <v>49.06382966740797</v>
+        <v>45.42968764308334</v>
       </c>
       <c r="D33" t="n">
-        <v>6.529068138026722</v>
+        <v>9.419711805952693</v>
       </c>
       <c r="E33" t="n">
-        <v>2.510213150325451</v>
+        <v>2.308518982886368</v>
       </c>
       <c r="F33" t="n">
-        <v>13.12431092806515</v>
+        <v>6.599939741723222</v>
       </c>
       <c r="G33" t="n">
-        <v>0.04088727601745192</v>
+        <v>0.2267527906870248</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.8716608878579698</v>
+        <v>-0.393157696697492</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.9108155963167801</v>
+        <v>-0.7022694249184027</v>
       </c>
       <c r="J33" t="n">
-        <v>-0.9277365586234132</v>
+        <v>-0.435264257380649</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.1513791871171555</v>
+        <v>-0.001272023257265084</v>
       </c>
       <c r="L33" t="n">
-        <v>-0.5506299116050195</v>
+        <v>-0.2674518779368948</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.09429478359999321</v>
+        <v>-0.00284094030909135</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>97.57372276455969</v>
+        <v>52.65913480385921</v>
       </c>
       <c r="B34" t="n">
-        <v>140.6129163747106</v>
+        <v>196.7569628756241</v>
       </c>
       <c r="C34" t="n">
-        <v>48.48148513397079</v>
+        <v>45.4357535808355</v>
       </c>
       <c r="D34" t="n">
-        <v>6.099194633090689</v>
+        <v>9.89769268610155</v>
       </c>
       <c r="E34" t="n">
-        <v>2.570395810339836</v>
+        <v>2.526091602190318</v>
       </c>
       <c r="F34" t="n">
-        <v>14.90983781955458</v>
+        <v>6.34864372936747</v>
       </c>
       <c r="G34" t="n">
-        <v>0.03210281787736567</v>
+        <v>0.2689175111109504</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.8958434326817142</v>
+        <v>-0.3068309033084168</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.9245828194473458</v>
+        <v>-0.6709014932168821</v>
       </c>
       <c r="J34" t="n">
-        <v>-0.9451293335053977</v>
+        <v>-0.3259771668276962</v>
       </c>
       <c r="K34" t="n">
-        <v>-0.2496613116984546</v>
+        <v>-0.06437519010042682</v>
       </c>
       <c r="L34" t="n">
-        <v>-0.6038825128611299</v>
+        <v>-0.2501963354774969</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.06539658378161038</v>
+        <v>-0.004164417636837864</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>84.41604527760347</v>
+        <v>51.44461271842809</v>
       </c>
       <c r="B35" t="n">
-        <v>159.4961131394766</v>
+        <v>116.5612977122502</v>
       </c>
       <c r="C35" t="n">
-        <v>48.83391861241822</v>
+        <v>46.31774368938124</v>
       </c>
       <c r="D35" t="n">
-        <v>7.835375165026395</v>
+        <v>9.85110247424355</v>
       </c>
       <c r="E35" t="n">
-        <v>4.225955665102217</v>
+        <v>2.953832014610157</v>
       </c>
       <c r="F35" t="n">
-        <v>11.97058529141586</v>
+        <v>6.205385873747693</v>
       </c>
       <c r="G35" t="n">
-        <v>0.05155956663909372</v>
+        <v>0.2936280016012918</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8441860739020732</v>
+        <v>-0.2684254592913067</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8958005129125242</v>
+        <v>-0.6595253201777381</v>
       </c>
       <c r="J35" t="n">
-        <v>-0.9066153743241468</v>
+        <v>-0.2784936527193365</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.2885133125446862</v>
+        <v>-0.07501611712995855</v>
       </c>
       <c r="L35" t="n">
-        <v>-0.5055937445495007</v>
+        <v>-0.2511887305035054</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.0804500765808971</v>
+        <v>-0.1965986231377254</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>70.23150720019689</v>
+        <v>98.22690009082312</v>
       </c>
       <c r="B36" t="n">
-        <v>136.9391988216407</v>
+        <v>97.66377133559783</v>
       </c>
       <c r="C36" t="n">
-        <v>48.88951901262052</v>
+        <v>45.43286333058408</v>
       </c>
       <c r="D36" t="n">
-        <v>7.807612961481989</v>
+        <v>6.862279074479425</v>
       </c>
       <c r="E36" t="n">
-        <v>4.191529502595198</v>
+        <v>2.71168912986044</v>
       </c>
       <c r="F36" t="n">
-        <v>8.887462810702186</v>
+        <v>15.3238534446216</v>
       </c>
       <c r="G36" t="n">
-        <v>0.09595505266817034</v>
+        <v>0.03099272305111439</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.737926390770857</v>
+        <v>-0.8839013874464055</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8434013673125907</v>
+        <v>-0.9176363475048256</v>
       </c>
       <c r="J36" t="n">
-        <v>-0.8143396225272779</v>
+        <v>-0.9367452376672789</v>
       </c>
       <c r="K36" t="n">
-        <v>-0.002362111506065893</v>
+        <v>-0.2598943200502684</v>
       </c>
       <c r="L36" t="n">
-        <v>-0.3996342560242792</v>
+        <v>-0.5748666631471148</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.08424717276879921</v>
+        <v>-0.003533817581981152</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>48.30808335210256</v>
+        <v>84.44688393742766</v>
       </c>
       <c r="B37" t="n">
-        <v>149.0905708118713</v>
+        <v>170.4166789899257</v>
       </c>
       <c r="C37" t="n">
-        <v>48.94155104886693</v>
+        <v>45.43467919141085</v>
       </c>
       <c r="D37" t="n">
-        <v>9.386430754428851</v>
+        <v>7.660400593516849</v>
       </c>
       <c r="E37" t="n">
-        <v>4.232004009300398</v>
+        <v>2.972550795872313</v>
       </c>
       <c r="F37" t="n">
-        <v>5.640440952604507</v>
+        <v>11.96106257841659</v>
       </c>
       <c r="G37" t="n">
-        <v>0.3768952212947216</v>
+        <v>0.05046508280262398</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.2206559242059954</v>
+        <v>-0.8230330772311071</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.6411654271396938</v>
+        <v>-0.8847607328937029</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.2116784941793692</v>
+        <v>-0.8896557614783205</v>
       </c>
       <c r="K37" t="n">
-        <v>-0.007615933819434377</v>
+        <v>-0.1142591750557408</v>
       </c>
       <c r="L37" t="n">
-        <v>-0.2358647511599772</v>
+        <v>-0.476684048054172</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.0878005760853431</v>
+        <v>-0.003930005398730951</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>88.15824375503391</v>
+        <v>55.88203192583285</v>
       </c>
       <c r="B38" t="n">
-        <v>147.8493949423531</v>
+        <v>196.1658806747618</v>
       </c>
       <c r="C38" t="n">
-        <v>48.78078256602937</v>
+        <v>47.10091904403291</v>
       </c>
       <c r="D38" t="n">
-        <v>6.278553224460771</v>
+        <v>9.383183156690929</v>
       </c>
       <c r="E38" t="n">
-        <v>2.335194772176423</v>
+        <v>3.512720395486916</v>
       </c>
       <c r="F38" t="n">
-        <v>12.48367930459801</v>
+        <v>6.801321973163432</v>
       </c>
       <c r="G38" t="n">
-        <v>0.0443254640746781</v>
+        <v>0.2158506752707584</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.8623018514660238</v>
+        <v>-0.4177070783974852</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9056943995076809</v>
+        <v>-0.7112639305146304</v>
       </c>
       <c r="J38" t="n">
-        <v>-0.9207135584510293</v>
+        <v>-0.4652719263349387</v>
       </c>
       <c r="K38" t="n">
-        <v>-0.006886597985444665</v>
+        <v>-0.03967956665411604</v>
       </c>
       <c r="L38" t="n">
-        <v>-0.5335482281191826</v>
+        <v>-0.273159477471559</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.0768212775354023</v>
+        <v>-0.3674732459708178</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>60.51370057439696</v>
+        <v>48.11132239581931</v>
       </c>
       <c r="B39" t="n">
-        <v>173.6112225050784</v>
+        <v>176.2487786533306</v>
       </c>
       <c r="C39" t="n">
-        <v>48.89385523692785</v>
+        <v>45.43085757499797</v>
       </c>
       <c r="D39" t="n">
-        <v>8.550871119292085</v>
+        <v>9.903557192957193</v>
       </c>
       <c r="E39" t="n">
-        <v>4.302946214801214</v>
+        <v>2.139326937111849</v>
       </c>
       <c r="F39" t="n">
-        <v>7.291739809386582</v>
+        <v>5.701935422719909</v>
       </c>
       <c r="G39" t="n">
-        <v>0.1634031852526271</v>
+        <v>0.3760829506437879</v>
       </c>
       <c r="H39" t="n">
-        <v>-0.5970220017174044</v>
+        <v>-0.09623907292046537</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.7818408525369069</v>
+        <v>-0.5990961566841657</v>
       </c>
       <c r="J39" t="n">
-        <v>-0.6716371371896314</v>
+        <v>-0.04121969346752014</v>
       </c>
       <c r="K39" t="n">
-        <v>-0.006620200217503149</v>
+        <v>-0.00748420965420495</v>
       </c>
       <c r="L39" t="n">
-        <v>-0.3270415629074773</v>
+        <v>-0.2177931720702126</v>
       </c>
       <c r="M39" t="n">
-        <v>-0.08454330482409621</v>
+        <v>-0.00309619818137527</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>77.31989311067517</v>
+        <v>87.49289680422174</v>
       </c>
       <c r="B40" t="n">
-        <v>161.258368704498</v>
+        <v>170.8048918086937</v>
       </c>
       <c r="C40" t="n">
-        <v>49.27817779491192</v>
+        <v>45.43379579230056</v>
       </c>
       <c r="D40" t="n">
-        <v>8.017647508309365</v>
+        <v>7.371954073493161</v>
       </c>
       <c r="E40" t="n">
-        <v>2.556917858398256</v>
+        <v>2.821357674533096</v>
       </c>
       <c r="F40" t="n">
-        <v>10.4180390608545</v>
+        <v>12.63066479923404</v>
       </c>
       <c r="G40" t="n">
-        <v>0.06921144536385487</v>
+        <v>0.04488148940462081</v>
       </c>
       <c r="H40" t="n">
-        <v>-0.8004741624886307</v>
+        <v>-0.8398564410453545</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.8733494239079305</v>
+        <v>-0.8935333329727372</v>
       </c>
       <c r="J40" t="n">
-        <v>-0.870528597454074</v>
+        <v>-0.9033011304864207</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.1938159295531539</v>
+        <v>-0.1133450387999136</v>
       </c>
       <c r="L40" t="n">
-        <v>-0.4525849930482788</v>
+        <v>-0.4983868897300799</v>
       </c>
       <c r="M40" t="n">
-        <v>-0.1065860558276737</v>
+        <v>-0.00373726377466882</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>90.24500491190878</v>
+        <v>60.4955998260823</v>
       </c>
       <c r="B41" t="n">
-        <v>149.3443614001581</v>
+        <v>103.9141265861137</v>
       </c>
       <c r="C41" t="n">
-        <v>49.99707655336091</v>
+        <v>45.43231571081027</v>
       </c>
       <c r="D41" t="n">
-        <v>6.223625147756073</v>
+        <v>8.93736330611258</v>
       </c>
       <c r="E41" t="n">
-        <v>2.641807092101976</v>
+        <v>2.506544388067351</v>
       </c>
       <c r="F41" t="n">
-        <v>13.00800150761086</v>
+        <v>7.366447465755174</v>
       </c>
       <c r="G41" t="n">
-        <v>0.04111781146319404</v>
+        <v>0.1606468348319246</v>
       </c>
       <c r="H41" t="n">
-        <v>-0.8709306544290567</v>
+        <v>-0.5448386908274035</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.9104340121364175</v>
+        <v>-0.7618783376994903</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.9271996228294858</v>
+        <v>-0.6157073668720506</v>
       </c>
       <c r="K41" t="n">
-        <v>-0.07743831526670127</v>
+        <v>-0.02515662399840953</v>
       </c>
       <c r="L41" t="n">
-        <v>-0.549136479470769</v>
+        <v>-0.3287169986956173</v>
       </c>
       <c r="M41" t="n">
-        <v>-0.08635461683243224</v>
+        <v>-0.003414336904059151</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>57.38549365591368</v>
+        <v>52.28327739549301</v>
       </c>
       <c r="B42" t="n">
-        <v>174.2586901911855</v>
+        <v>170.9667656767486</v>
       </c>
       <c r="C42" t="n">
-        <v>48.79853839119161</v>
+        <v>45.43087756932606</v>
       </c>
       <c r="D42" t="n">
-        <v>9.356569864502722</v>
+        <v>9.630365720971453</v>
       </c>
       <c r="E42" t="n">
-        <v>4.991417063608823</v>
+        <v>2.632865659387566</v>
       </c>
       <c r="F42" t="n">
-        <v>6.97242529421128</v>
+        <v>6.227038896848003</v>
       </c>
       <c r="G42" t="n">
-        <v>0.199625483588816</v>
+        <v>0.2752498225196601</v>
       </c>
       <c r="H42" t="n">
-        <v>-0.5289105728563189</v>
+        <v>-0.2926905921976719</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.7541274039889933</v>
+        <v>-0.6660010534687761</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.5958950593252209</v>
+        <v>-0.3077894467737767</v>
       </c>
       <c r="K42" t="n">
-        <v>-0.1247495581492774</v>
+        <v>-0.006730959844320126</v>
       </c>
       <c r="L42" t="n">
-        <v>-0.3036736390967254</v>
+        <v>-0.2475183514428877</v>
       </c>
       <c r="M42" t="n">
-        <v>-0.07803386909573769</v>
+        <v>-0.003100560580232836</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>57.5585881562565</v>
+        <v>89.39247138786676</v>
       </c>
       <c r="B43" t="n">
-        <v>157.4920531583122</v>
+        <v>95.40707811637617</v>
       </c>
       <c r="C43" t="n">
-        <v>49.93231047871087</v>
+        <v>45.42707857217693</v>
       </c>
       <c r="D43" t="n">
-        <v>9.356569864502722</v>
+        <v>6.823943526259413</v>
       </c>
       <c r="E43" t="n">
-        <v>4.998106972639432</v>
+        <v>2.347879209972727</v>
       </c>
       <c r="F43" t="n">
-        <v>7.026996479639222</v>
+        <v>12.97098563225435</v>
       </c>
       <c r="G43" t="n">
-        <v>0.1976989541998014</v>
+        <v>0.04174543186755754</v>
       </c>
       <c r="H43" t="n">
-        <v>-0.5328725762980391</v>
+        <v>-0.8493286737775632</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.755665773443931</v>
+        <v>-0.8986108726559554</v>
       </c>
       <c r="J43" t="n">
-        <v>-0.6003659601150365</v>
+        <v>-0.9107950476072751</v>
       </c>
       <c r="K43" t="n">
-        <v>-0.146756945130448</v>
+        <v>-0.01604259968357311</v>
       </c>
       <c r="L43" t="n">
-        <v>-0.3049666670841555</v>
+        <v>-0.5119213586385506</v>
       </c>
       <c r="M43" t="n">
-        <v>-0.08901666782852428</v>
+        <v>-0.002271688474966699</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>75.7978165586849</v>
+        <v>94.03081353207207</v>
       </c>
       <c r="B44" t="n">
-        <v>143.7892876992482</v>
+        <v>183.8205319451434</v>
       </c>
       <c r="C44" t="n">
-        <v>48.8920712916517</v>
+        <v>45.43614966481296</v>
       </c>
       <c r="D44" t="n">
-        <v>8.263785515952941</v>
+        <v>6.911530583689007</v>
       </c>
       <c r="E44" t="n">
-        <v>2.903034716151731</v>
+        <v>3.536728232685387</v>
       </c>
       <c r="F44" t="n">
-        <v>10.14310928176581</v>
+        <v>14.19557165844579</v>
       </c>
       <c r="G44" t="n">
-        <v>0.07415246877400733</v>
+        <v>0.03554944741835125</v>
       </c>
       <c r="H44" t="n">
-        <v>-0.7888310711554375</v>
+        <v>-0.8690483956046988</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.8675688318167736</v>
+        <v>-0.9093084624778444</v>
       </c>
       <c r="J44" t="n">
-        <v>-0.860436966470647</v>
+        <v>-0.9258626072386981</v>
       </c>
       <c r="K44" t="n">
-        <v>-0.2080534919013655</v>
+        <v>-0.1614623792418227</v>
       </c>
       <c r="L44" t="n">
-        <v>-0.4412149750706043</v>
+        <v>-0.5449695464160134</v>
       </c>
       <c r="M44" t="n">
-        <v>-0.08442147455339971</v>
+        <v>-0.004250835959191263</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>74.70225706205738</v>
+        <v>55.72341512135279</v>
       </c>
       <c r="B45" t="n">
-        <v>178.1436933585257</v>
+        <v>178.7098536715537</v>
       </c>
       <c r="C45" t="n">
-        <v>47.45485319485591</v>
+        <v>45.42968764308334</v>
       </c>
       <c r="D45" t="n">
-        <v>7.810287804656588</v>
+        <v>9.438671059871826</v>
       </c>
       <c r="E45" t="n">
-        <v>2.240266878857672</v>
+        <v>2.308518982886368</v>
       </c>
       <c r="F45" t="n">
-        <v>9.790585057436632</v>
+        <v>6.705228024268615</v>
       </c>
       <c r="G45" t="n">
-        <v>0.07762133473005374</v>
+        <v>0.2174001308643646</v>
       </c>
       <c r="H45" t="n">
-        <v>-0.7801615669216109</v>
+        <v>-0.4133415667157519</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.8634120979397492</v>
+        <v>-0.7097335711454306</v>
       </c>
       <c r="J45" t="n">
-        <v>-0.8528439398978002</v>
+        <v>-0.4600501366254831</v>
       </c>
       <c r="K45" t="n">
-        <v>-0.06459951136347955</v>
+        <v>-0.0142632781007983</v>
       </c>
       <c r="L45" t="n">
-        <v>-0.4330310692374984</v>
+        <v>-0.2720293327396386</v>
       </c>
       <c r="M45" t="n">
-        <v>-0.08737011747051319</v>
+        <v>-0.00284094030909135</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>53.78569923244886</v>
+        <v>82.92721014217841</v>
       </c>
       <c r="B46" t="n">
-        <v>141.804019009997</v>
+        <v>143.4258042297731</v>
       </c>
       <c r="C46" t="n">
-        <v>49.07587582893554</v>
+        <v>45.43387642684113</v>
       </c>
       <c r="D46" t="n">
-        <v>9.309692973051547</v>
+        <v>7.708030399468655</v>
       </c>
       <c r="E46" t="n">
-        <v>2.327854673676704</v>
+        <v>3.496934291531045</v>
       </c>
       <c r="F46" t="n">
-        <v>6.405276898630354</v>
+        <v>11.61313047636098</v>
       </c>
       <c r="G46" t="n">
-        <v>0.2528878343119498</v>
+        <v>0.05358663221135103</v>
       </c>
       <c r="H46" t="n">
-        <v>-0.4310830838985169</v>
+        <v>-0.8137384426904311</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.7164863094501511</v>
+        <v>-0.8800168640571512</v>
       </c>
       <c r="J46" t="n">
-        <v>-0.4809511973578108</v>
+        <v>-0.8819349415839118</v>
       </c>
       <c r="K46" t="n">
-        <v>-0.07057613391611234</v>
+        <v>-0.09335223345110877</v>
       </c>
       <c r="L46" t="n">
-        <v>-0.2767829237399928</v>
+        <v>-0.4658563722630211</v>
       </c>
       <c r="M46" t="n">
-        <v>-0.09512591954988833</v>
+        <v>-0.003754856765337128</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>96.04971859255025</v>
+        <v>85.57315178045185</v>
       </c>
       <c r="B47" t="n">
-        <v>176.8307814173172</v>
+        <v>170.4166789899257</v>
       </c>
       <c r="C47" t="n">
-        <v>48.48248521515497</v>
+        <v>45.43468721809046</v>
       </c>
       <c r="D47" t="n">
-        <v>6.099756262102415</v>
+        <v>7.660400593516849</v>
       </c>
       <c r="E47" t="n">
-        <v>2.51579926766938</v>
+        <v>2.972550795872313</v>
       </c>
       <c r="F47" t="n">
-        <v>14.49159012242054</v>
+        <v>12.23177283258728</v>
       </c>
       <c r="G47" t="n">
-        <v>0.0337204691160388</v>
+        <v>0.04832394797162548</v>
       </c>
       <c r="H47" t="n">
-        <v>-0.8912737394356081</v>
+        <v>-0.8294955157847012</v>
       </c>
       <c r="I47" t="n">
-        <v>-0.9219360591372273</v>
+        <v>-0.8880923896024849</v>
       </c>
       <c r="J47" t="n">
-        <v>-0.9419351675438066</v>
+        <v>-0.8949456278857224</v>
       </c>
       <c r="K47" t="n">
-        <v>-0.1999256195957918</v>
+        <v>-0.1381019496705649</v>
       </c>
       <c r="L47" t="n">
-        <v>-0.5924980954274994</v>
+        <v>-0.4847087064357194</v>
       </c>
       <c r="M47" t="n">
-        <v>-0.06537682279228609</v>
+        <v>-0.003931756674282194</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>48.14288028489202</v>
+        <v>51.34296158855921</v>
       </c>
       <c r="B48" t="n">
-        <v>148.9992248221691</v>
+        <v>177.2165455723394</v>
       </c>
       <c r="C48" t="n">
-        <v>49.82797980128763</v>
+        <v>45.43612253402051</v>
       </c>
       <c r="D48" t="n">
-        <v>9.386430754428851</v>
+        <v>9.89769268610155</v>
       </c>
       <c r="E48" t="n">
-        <v>4.432615580561897</v>
+        <v>2.526091602190318</v>
       </c>
       <c r="F48" t="n">
-        <v>5.632918927475822</v>
+        <v>6.155147159389701</v>
       </c>
       <c r="G48" t="n">
-        <v>0.3820703720982627</v>
+        <v>0.2952782502224104</v>
       </c>
       <c r="H48" t="n">
-        <v>-0.2126210547725347</v>
+        <v>-0.2534218482562915</v>
       </c>
       <c r="I48" t="n">
-        <v>-0.6383909620117328</v>
+        <v>-0.6521558302711196</v>
       </c>
       <c r="J48" t="n">
-        <v>-0.2008218222496089</v>
+        <v>-0.2561518358655389</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.02284151691362042</v>
+        <v>-0.04761207807049512</v>
       </c>
       <c r="L48" t="n">
-        <v>-0.2346306727283145</v>
+        <v>-0.2408186013184843</v>
       </c>
       <c r="M48" t="n">
-        <v>-0.09436250077773378</v>
+        <v>-0.004244916513565927</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>62.59197377647413</v>
+        <v>86.10283401026548</v>
       </c>
       <c r="B49" t="n">
-        <v>136.9391988216407</v>
+        <v>151.2562478150863</v>
       </c>
       <c r="C49" t="n">
-        <v>48.83012348540553</v>
+        <v>45.43588834845047</v>
       </c>
       <c r="D49" t="n">
-        <v>9.010901292541202</v>
+        <v>7.711355831349658</v>
       </c>
       <c r="E49" t="n">
-        <v>2.036969931559777</v>
+        <v>3.740576412532419</v>
       </c>
       <c r="F49" t="n">
-        <v>7.763644441823619</v>
+        <v>12.37287909637572</v>
       </c>
       <c r="G49" t="n">
-        <v>0.1454880842571794</v>
+        <v>0.04737550505411135</v>
       </c>
       <c r="H49" t="n">
-        <v>-0.6340721604398145</v>
+        <v>-0.8324041788439873</v>
       </c>
       <c r="I49" t="n">
-        <v>-0.7972250405419742</v>
+        <v>-0.8895965007512119</v>
       </c>
       <c r="J49" t="n">
-        <v>-0.7109572998326406</v>
+        <v>-0.8973035179238679</v>
       </c>
       <c r="K49" t="n">
-        <v>-0.135141004167997</v>
+        <v>-0.160516274504578</v>
       </c>
       <c r="L49" t="n">
-        <v>-0.3425664086448603</v>
+        <v>-0.4884826923231416</v>
       </c>
       <c r="M49" t="n">
-        <v>-0.08019089746959561</v>
+        <v>-0.004193821480102666</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>51.19019131661813</v>
+        <v>71.47279083845787</v>
       </c>
       <c r="B50" t="n">
-        <v>160.4692268368859</v>
+        <v>170.0691598600669</v>
       </c>
       <c r="C50" t="n">
-        <v>48.84418284869759</v>
+        <v>45.42163495762825</v>
       </c>
       <c r="D50" t="n">
-        <v>9.224916390953798</v>
+        <v>8.362951166394636</v>
       </c>
       <c r="E50" t="n">
-        <v>4.46325674420302</v>
+        <v>2.587207781494816</v>
       </c>
       <c r="F50" t="n">
-        <v>5.997541140525764</v>
+        <v>9.273011712817551</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3031234984345434</v>
+        <v>0.08889345672365644</v>
       </c>
       <c r="H50" t="n">
-        <v>-0.3427848652182754</v>
+        <v>-0.7154193633012041</v>
       </c>
       <c r="I50" t="n">
-        <v>-0.6840991251045571</v>
+        <v>-0.8329365082943117</v>
       </c>
       <c r="J50" t="n">
-        <v>-0.37143879951308</v>
+        <v>-0.7931499867707713</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.01190775299916864</v>
+        <v>-0.02554072621954133</v>
       </c>
       <c r="L50" t="n">
-        <v>-0.257394298624125</v>
+        <v>-0.3842436347240122</v>
       </c>
       <c r="M50" t="n">
-        <v>-0.08115104801826657</v>
+        <v>-0.001083990755253866</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>74.89636973047548</v>
+        <v>47.87708050739973</v>
       </c>
       <c r="B51" t="n">
-        <v>178.1436933585257</v>
+        <v>161.8887047023945</v>
       </c>
       <c r="C51" t="n">
-        <v>47.45485319485591</v>
+        <v>45.43611663792249</v>
       </c>
       <c r="D51" t="n">
-        <v>7.821927707158391</v>
+        <v>9.898274078037646</v>
       </c>
       <c r="E51" t="n">
-        <v>2.240266878857672</v>
+        <v>2.274100503950476</v>
       </c>
       <c r="F51" t="n">
-        <v>9.834256747866281</v>
+        <v>5.669133714684039</v>
       </c>
       <c r="G51" t="n">
-        <v>0.07694579745542193</v>
+        <v>0.382988613994783</v>
       </c>
       <c r="H51" t="n">
-        <v>-0.7817684823769213</v>
+        <v>-0.08317434647620185</v>
       </c>
       <c r="I51" t="n">
-        <v>-0.8641904655156487</v>
+        <v>-0.5948145720811356</v>
       </c>
       <c r="J51" t="n">
-        <v>-0.8542635543416277</v>
+        <v>-0.02276189784082879</v>
       </c>
       <c r="K51" t="n">
-        <v>-0.07133433029622326</v>
+        <v>-0.003555894617432436</v>
       </c>
       <c r="L51" t="n">
-        <v>-0.4344811044060464</v>
+        <v>-0.216124198615223</v>
       </c>
       <c r="M51" t="n">
-        <v>-0.08737011747051319</v>
+        <v>-0.004243630092178735</v>
       </c>
     </row>
   </sheetData>
